--- a/kalarakal.xlsx
+++ b/kalarakal.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chella\eclipse-workspace\mavenCrm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164BB1AF-A202-451B-99E1-DAA7673F9ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BBB69B-4EF3-4D67-9B0D-40700AA09889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="468">
   <si>
     <t>Status</t>
   </si>
@@ -1285,9 +1285,6 @@
     <t>Gold – Cash (Fixed Amount Scheme)</t>
   </si>
   <si>
-    <t>Silver – Cash (Fixed Amount Scheme)</t>
-  </si>
-  <si>
     <t>Silver-GRAM FLEXIBLE</t>
   </si>
   <si>
@@ -1405,9 +1402,6 @@
     <t>Developer</t>
   </si>
   <si>
-    <t>26-F-AMT-52</t>
-  </si>
-  <si>
     <t>FAS-not allocated</t>
   </si>
   <si>
@@ -1423,9 +1417,6 @@
     <t>https://staging.kallarackalsjewellers.com/admin/index.php/admin/login</t>
   </si>
   <si>
-    <t>10 Sec</t>
-  </si>
-  <si>
     <t>HDFC</t>
   </si>
   <si>
@@ -1438,15 +1429,17 @@
     <t>52 Sec</t>
   </si>
   <si>
-    <t>11 Sec</t>
+    <t>9 Sec</t>
+  </si>
+  <si>
+    <t>26-FAS-40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="44" x14ac:knownFonts="1">
+  <fonts count="43" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1693,7 +1686,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="10"/>
+      <color indexed="17"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1707,12 +1700,6 @@
       <sz val="11"/>
       <color indexed="17"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1736,7 +1723,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
@@ -1784,7 +1771,6 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2069,136 +2055,136 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.90625"/>
+    <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>408</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>469</v>
+      <c r="D2" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s" s="0">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>409</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s" s="0">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>409</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="D4" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s" s="0">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>412</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
+      <c r="A6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s" s="0">
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>414</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>452</v>
+      <c r="D6" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="0">
+      <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s" s="0">
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
         <v>414</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="D7" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s" s="0">
+      <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s" s="0">
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D8" t="s">
         <v>454</v>
       </c>
-      <c r="D8" t="s" s="0">
-        <v>455</v>
-      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s" s="0">
+      <c r="A9" t="s">
         <v>28</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s" s="0">
-        <v>467</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>468</v>
+      <c r="C9" t="s">
+        <v>464</v>
+      </c>
+      <c r="D9" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -2211,233 +2197,233 @@
   <dimension ref="A5:AQ13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.81640625"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="B5" t="s" s="0">
-        <v>438</v>
+      <c r="B5" t="s">
+        <v>437</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>442</v>
-      </c>
-      <c r="E5" t="s" s="0">
+      <c r="D5" t="s">
+        <v>441</v>
+      </c>
+      <c r="E5" t="s">
         <v>407</v>
       </c>
-      <c r="F5" t="s" s="0">
+      <c r="F5" t="s">
         <v>211</v>
       </c>
-      <c r="G5" s="0">
+      <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="0">
+      <c r="H5">
         <v>10000</v>
       </c>
-      <c r="N5" s="0">
+      <c r="N5">
         <v>10000</v>
       </c>
-      <c r="O5" s="0">
+      <c r="O5">
         <v>73833</v>
       </c>
-      <c r="P5" t="s" s="0">
+      <c r="P5" t="s">
         <v>9</v>
       </c>
       <c r="S5" s="2"/>
-      <c r="U5" s="0">
+      <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" t="s" s="0">
+      <c r="V5" t="s">
         <v>12</v>
       </c>
       <c r="W5" s="2">
         <v>46170</v>
       </c>
-      <c r="X5" t="s" s="0">
+      <c r="X5" t="s">
         <v>366</v>
       </c>
-      <c r="Y5" s="0">
+      <c r="Y5">
         <v>93212</v>
       </c>
-      <c r="Z5" s="0">
+      <c r="Z5">
         <v>2093005</v>
       </c>
-      <c r="AA5" s="0">
+      <c r="AA5">
         <v>10000</v>
       </c>
-      <c r="AB5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AD5" s="0">
+      <c r="AB5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD5">
         <v>0</v>
       </c>
-      <c r="AE5" s="0">
+      <c r="AE5">
         <v>0</v>
       </c>
-      <c r="AF5" t="s" s="0">
-        <v>440</v>
-      </c>
-      <c r="AG5" s="0">
+      <c r="AF5" t="s">
+        <v>439</v>
+      </c>
+      <c r="AG5">
         <v>30000</v>
       </c>
-      <c r="AI5" t="s" s="0">
-        <v>427</v>
-      </c>
-      <c r="AJ5" t="s" s="0">
+      <c r="AI5" t="s">
+        <v>426</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AK5" t="s">
         <v>448</v>
       </c>
-      <c r="AK5" t="s" s="0">
-        <v>449</v>
-      </c>
       <c r="AL5" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="AM5" t="s" s="0">
+        <v>432</v>
+      </c>
+      <c r="AM5" t="s">
         <v>383</v>
       </c>
-      <c r="AN5" t="s" s="0">
+      <c r="AN5" t="s">
         <v>383</v>
       </c>
-      <c r="AQ5" t="s" s="0">
-        <v>419</v>
+      <c r="AQ5" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="B6" t="s" s="0">
-        <v>439</v>
+      <c r="B6" t="s">
+        <v>438</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>443</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>422</v>
-      </c>
-      <c r="F6" t="s" s="0">
+      <c r="D6" t="s">
+        <v>442</v>
+      </c>
+      <c r="E6" t="s">
+        <v>421</v>
+      </c>
+      <c r="F6" t="s">
         <v>304</v>
       </c>
-      <c r="G6" s="0">
+      <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="0">
+      <c r="H6">
         <v>2000</v>
       </c>
-      <c r="N6" s="0">
+      <c r="N6">
         <v>5000</v>
       </c>
-      <c r="O6" s="0">
+      <c r="O6">
         <v>73834</v>
       </c>
-      <c r="P6" t="s" s="0">
+      <c r="P6" t="s">
         <v>9</v>
       </c>
       <c r="S6" s="2"/>
-      <c r="U6" s="0">
+      <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6" t="s" s="0">
+      <c r="V6" t="s">
         <v>12</v>
       </c>
       <c r="W6" s="2">
         <v>46171</v>
       </c>
-      <c r="X6" t="s" s="0">
+      <c r="X6" t="s">
         <v>366</v>
       </c>
-      <c r="Y6" s="0">
+      <c r="Y6">
         <v>93213</v>
       </c>
-      <c r="Z6" s="0">
+      <c r="Z6">
         <v>2093006</v>
       </c>
-      <c r="AA6" s="0">
+      <c r="AA6">
         <v>3000</v>
       </c>
-      <c r="AB6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AD6" s="0">
+      <c r="AB6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD6">
         <v>0</v>
       </c>
-      <c r="AE6" s="0">
+      <c r="AE6">
         <v>0</v>
       </c>
-      <c r="AF6" t="s" s="0">
-        <v>441</v>
-      </c>
-      <c r="AG6" s="0">
+      <c r="AF6" t="s">
+        <v>440</v>
+      </c>
+      <c r="AG6">
         <v>10000</v>
       </c>
-      <c r="AI6" t="s" s="0">
-        <v>428</v>
-      </c>
-      <c r="AJ6" t="s" s="0">
+      <c r="AI6" t="s">
+        <v>427</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>449</v>
+      </c>
+      <c r="AK6" t="s">
         <v>450</v>
       </c>
-      <c r="AK6" t="s" s="0">
-        <v>451</v>
-      </c>
       <c r="AL6" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="AM6" t="s" s="0">
+        <v>433</v>
+      </c>
+      <c r="AM6" t="s">
         <v>383</v>
       </c>
-      <c r="AN6" t="s" s="0">
+      <c r="AN6" t="s">
         <v>383</v>
       </c>
-      <c r="AQ6" t="s" s="0">
-        <v>424</v>
+      <c r="AQ6" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" s="38" t="s">
         <v>378</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="D10" s="0">
+      <c r="C10" t="s">
+        <v>422</v>
+      </c>
+      <c r="D10">
         <v>8925535099</v>
       </c>
-      <c r="E10" t="s" s="0">
-        <v>419</v>
-      </c>
-      <c r="H10" t="s" s="0">
+      <c r="E10" t="s">
+        <v>418</v>
+      </c>
+      <c r="H10" t="s">
         <v>304</v>
       </c>
-      <c r="I10" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="N10" t="s" s="0">
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" t="s">
         <v>339</v>
       </c>
-      <c r="O10" s="0">
+      <c r="O10">
         <v>30000</v>
       </c>
-      <c r="P10" t="s" s="0">
-        <v>453</v>
-      </c>
-      <c r="Q10" t="s" s="0">
+      <c r="P10" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q10" t="s">
         <v>383</v>
       </c>
-      <c r="R10" t="s" s="0">
+      <c r="R10" t="s">
         <v>383</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="T10" t="s" s="0">
+        <v>432</v>
+      </c>
+      <c r="T10" t="s">
         <v>383</v>
       </c>
-      <c r="U10" t="s" s="0">
+      <c r="U10" t="s">
         <v>383</v>
       </c>
     </row>
@@ -2445,46 +2431,46 @@
       <c r="A11" s="39" t="s">
         <v>378</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="C11" t="s" s="0">
+      <c r="C11" t="s">
+        <v>422</v>
+      </c>
+      <c r="D11">
+        <v>8925535099</v>
+      </c>
+      <c r="E11" t="s">
         <v>423</v>
       </c>
-      <c r="D11" s="0">
-        <v>8925535099</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="H11" t="s" s="0">
+      <c r="H11" t="s">
         <v>304</v>
       </c>
-      <c r="I11" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="N11" t="s" s="0">
+      <c r="I11" t="s">
+        <v>9</v>
+      </c>
+      <c r="N11" t="s">
         <v>339</v>
       </c>
-      <c r="O11" s="0">
+      <c r="O11">
         <v>10000</v>
       </c>
-      <c r="P11" t="s" s="0">
-        <v>428</v>
-      </c>
-      <c r="Q11" t="s" s="0">
+      <c r="P11" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q11" t="s">
         <v>383</v>
       </c>
-      <c r="R11" t="s" s="0">
+      <c r="R11" t="s">
         <v>383</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="T11" t="s" s="0">
+        <v>433</v>
+      </c>
+      <c r="T11" t="s">
         <v>383</v>
       </c>
-      <c r="U11" t="s" s="0">
+      <c r="U11" t="s">
         <v>383</v>
       </c>
     </row>
@@ -2492,43 +2478,43 @@
       <c r="A12" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>179</v>
       </c>
-      <c r="C12" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="D12" s="0">
+      <c r="C12" t="s">
+        <v>422</v>
+      </c>
+      <c r="D12">
         <v>8925535099</v>
       </c>
-      <c r="E12" t="s" s="0">
-        <v>420</v>
-      </c>
-      <c r="H12" t="s" s="0">
+      <c r="E12" t="s">
+        <v>419</v>
+      </c>
+      <c r="H12" t="s">
         <v>140</v>
       </c>
-      <c r="I12" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="N12" t="s" s="0">
+      <c r="I12" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" t="s">
         <v>339</v>
       </c>
-      <c r="P12" t="s" s="0">
-        <v>429</v>
-      </c>
-      <c r="Q12" t="s" s="0">
+      <c r="P12" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q12" t="s">
         <v>383</v>
       </c>
-      <c r="R12" t="s" s="0">
+      <c r="R12" t="s">
         <v>383</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="T12" t="s" s="0">
+        <v>434</v>
+      </c>
+      <c r="T12" t="s">
         <v>383</v>
       </c>
-      <c r="U12" t="s" s="0">
+      <c r="U12" t="s">
         <v>383</v>
       </c>
     </row>
@@ -2536,43 +2522,43 @@
       <c r="A13" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>193</v>
       </c>
-      <c r="C13" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="D13" s="0">
+      <c r="C13" t="s">
+        <v>422</v>
+      </c>
+      <c r="D13">
         <v>8925535099</v>
       </c>
-      <c r="E13" t="s" s="0">
-        <v>421</v>
-      </c>
-      <c r="H13" t="s" s="0">
+      <c r="E13" t="s">
+        <v>420</v>
+      </c>
+      <c r="H13" t="s">
         <v>194</v>
       </c>
-      <c r="I13" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="N13" t="s" s="0">
+      <c r="I13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" t="s">
         <v>339</v>
       </c>
-      <c r="P13" t="s" s="0">
-        <v>430</v>
-      </c>
-      <c r="Q13" t="s" s="0">
+      <c r="P13" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q13" t="s">
         <v>383</v>
       </c>
-      <c r="R13" t="s" s="0">
+      <c r="R13" t="s">
         <v>383</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="T13" t="s" s="0">
+        <v>435</v>
+      </c>
+      <c r="T13" t="s">
         <v>383</v>
       </c>
-      <c r="U13" t="s" s="0">
+      <c r="U13" t="s">
         <v>383</v>
       </c>
     </row>
@@ -2586,44 +2572,44 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="2" max="2" customWidth="true" width="5.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="62.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.90625" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>378</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E2" t="s" s="0">
+        <v>461</v>
+      </c>
+      <c r="E2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2637,29 +2623,29 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="10.0"/>
-    <col min="3" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="5" customWidth="true" width="8.0"/>
-    <col min="6" max="6" customWidth="true" width="25.0"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2667,16 +2653,16 @@
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2684,19 +2670,19 @@
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s" s="0">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2704,16 +2690,16 @@
       <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s" s="0">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2721,19 +2707,19 @@
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s" s="0">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>368</v>
       </c>
     </row>
@@ -2741,16 +2727,16 @@
       <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2764,29 +2750,29 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="10.0"/>
-    <col min="3" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="5" customWidth="true" width="8.0"/>
-    <col min="6" max="6" customWidth="true" width="25.0"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2794,16 +2780,16 @@
       <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2811,19 +2797,19 @@
       <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>37</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s" s="0">
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2831,16 +2817,16 @@
       <c r="A4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s" s="0">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2848,19 +2834,19 @@
       <c r="A5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s" s="0">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2868,16 +2854,16 @@
       <c r="A6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="C6" t="s">
         <v>42</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2891,29 +2877,29 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="10.0"/>
-    <col min="3" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="5" customWidth="true" width="8.0"/>
-    <col min="6" max="6" customWidth="true" width="25.0"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2921,16 +2907,16 @@
       <c r="A2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>44</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2938,19 +2924,19 @@
       <c r="A3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s" s="0">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2958,16 +2944,16 @@
       <c r="A4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>47</v>
       </c>
-      <c r="D4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s" s="0">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2975,19 +2961,19 @@
       <c r="A5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s">
         <v>48</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s" s="0">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2995,13 +2981,13 @@
       <c r="A6" s="19" t="s">
         <v>378</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3015,181 +3001,181 @@
   <dimension ref="A1:AR9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.6328125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.36328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="16.6328125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="8.6328125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="9.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="20.90625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="22.90625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="12.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="19.90625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.08984375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="10.26953125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="10.6328125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="7.36328125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="14.453125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="10.54296875"/>
-    <col min="26" max="27" bestFit="true" customWidth="true" width="11.81640625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="8.81640625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="13.6328125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="15.08984375"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="12.54296875"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="4.0"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="6.0"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="12.36328125"/>
-    <col min="38" max="38" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="25.36328125"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="22.6328125"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="13.81640625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="15.1796875"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="1" max="2" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>57</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>58</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>59</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>60</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>61</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>62</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>64</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>65</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="S1" t="s">
         <v>66</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="T1" t="s">
         <v>67</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="U1" t="s">
         <v>68</v>
       </c>
-      <c r="V1" t="s" s="0">
+      <c r="V1" t="s">
         <v>69</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="W1" t="s">
         <v>70</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="X1" t="s">
         <v>71</v>
       </c>
-      <c r="Y1" t="s" s="0">
+      <c r="Y1" t="s">
         <v>72</v>
       </c>
-      <c r="Z1" t="s" s="0">
+      <c r="Z1" t="s">
         <v>73</v>
       </c>
-      <c r="AA1" t="s" s="0">
+      <c r="AA1" t="s">
         <v>74</v>
       </c>
-      <c r="AB1" t="s" s="0">
+      <c r="AB1" t="s">
         <v>75</v>
       </c>
-      <c r="AC1" t="s" s="0">
+      <c r="AC1" t="s">
         <v>76</v>
       </c>
-      <c r="AD1" t="s" s="0">
+      <c r="AD1" t="s">
         <v>77</v>
       </c>
-      <c r="AE1" t="s" s="0">
+      <c r="AE1" t="s">
         <v>78</v>
       </c>
-      <c r="AF1" t="s" s="0">
+      <c r="AF1" t="s">
         <v>79</v>
       </c>
-      <c r="AG1" t="s" s="0">
+      <c r="AG1" t="s">
         <v>80</v>
       </c>
-      <c r="AH1" t="s" s="0">
+      <c r="AH1" t="s">
         <v>82</v>
       </c>
-      <c r="AI1" t="s" s="0">
+      <c r="AI1" t="s">
         <v>3</v>
       </c>
-      <c r="AJ1" t="s" s="0">
+      <c r="AJ1" t="s">
         <v>4</v>
       </c>
-      <c r="AK1" t="s" s="0">
+      <c r="AK1" t="s">
         <v>83</v>
       </c>
-      <c r="AL1" t="s" s="0">
+      <c r="AL1" t="s">
         <v>84</v>
       </c>
-      <c r="AM1" t="s" s="0">
+      <c r="AM1" t="s">
         <v>85</v>
       </c>
-      <c r="AN1" t="s" s="0">
+      <c r="AN1" t="s">
         <v>86</v>
       </c>
-      <c r="AO1" t="s" s="0">
+      <c r="AO1" t="s">
         <v>396</v>
       </c>
-      <c r="AP1" t="s" s="0">
+      <c r="AP1" t="s">
         <v>397</v>
       </c>
-      <c r="AQ1" t="s" s="0">
+      <c r="AQ1" t="s">
         <v>398</v>
       </c>
-      <c r="AR1" t="s" s="0">
+      <c r="AR1" t="s">
         <v>399</v>
       </c>
     </row>
@@ -3298,10 +3284,10 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
-      <c r="AQ2" t="s" s="0">
+      <c r="AQ2" t="s">
         <v>402</v>
       </c>
-      <c r="AR2" t="s" s="0">
+      <c r="AR2" t="s">
         <v>383</v>
       </c>
     </row>
@@ -3412,10 +3398,10 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
       <c r="AN3" s="3"/>
-      <c r="AO3" t="s" s="0">
+      <c r="AO3" t="s">
         <v>400</v>
       </c>
-      <c r="AR3" t="s" s="0">
+      <c r="AR3" t="s">
         <v>383</v>
       </c>
     </row>
@@ -4040,10 +4026,10 @@
       <c r="AN9" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AP9" t="s" s="0">
+      <c r="AP9" t="s">
         <v>401</v>
       </c>
-      <c r="AR9" t="s" s="0">
+      <c r="AR9" t="s">
         <v>383</v>
       </c>
     </row>
@@ -4061,137 +4047,137 @@
   <dimension ref="A1:AG9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="8.6328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="8.81640625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="3.6328125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.36328125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="5.81640625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.08984375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="14.7265625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="10.6328125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.26953125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.6328125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="12.453125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="26.90625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="13.08984375"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="12.36328125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="11.08984375"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="20.1796875"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="4.0"/>
-    <col min="26" max="27" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.1796875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="16.08984375"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="12.7265625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="14.0"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="6.0"/>
+    <col min="1" max="2" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>231</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>232</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>233</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>234</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>235</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>236</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>237</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>65</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>66</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>67</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>61</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>57</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="S1" t="s">
         <v>238</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="T1" t="s">
         <v>239</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="U1" t="s">
         <v>82</v>
       </c>
-      <c r="V1" t="s" s="0">
+      <c r="V1" t="s">
         <v>240</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="W1" t="s">
         <v>241</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="X1" t="s">
         <v>242</v>
       </c>
-      <c r="Y1" t="s" s="0">
+      <c r="Y1" t="s">
         <v>3</v>
       </c>
-      <c r="Z1" t="s" s="0">
+      <c r="Z1" t="s">
         <v>243</v>
       </c>
-      <c r="AA1" t="s" s="0">
+      <c r="AA1" t="s">
         <v>244</v>
       </c>
-      <c r="AB1" t="s" s="0">
+      <c r="AB1" t="s">
         <v>245</v>
       </c>
-      <c r="AC1" t="s" s="0">
+      <c r="AC1" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" t="s" s="0">
+      <c r="AD1" t="s">
         <v>35</v>
       </c>
-      <c r="AE1" t="s" s="0">
+      <c r="AE1" t="s">
         <v>246</v>
       </c>
-      <c r="AF1" t="s" s="0">
+      <c r="AF1" t="s">
         <v>247</v>
       </c>
-      <c r="AG1" t="s" s="0">
+      <c r="AG1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4199,97 +4185,97 @@
       <c r="A2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>248</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>90</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>249</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>250</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>251</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>203</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>204</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>99</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>100</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>203</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>252</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>91</v>
       </c>
-      <c r="S2" t="s" s="0">
+      <c r="S2" t="s">
         <v>253</v>
       </c>
-      <c r="T2" t="s" s="0">
+      <c r="T2" t="s">
         <v>254</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>255</v>
       </c>
-      <c r="V2" t="s" s="0">
+      <c r="V2" t="s">
         <v>367</v>
       </c>
-      <c r="W2" t="s" s="0">
+      <c r="W2" t="s">
         <v>405</v>
       </c>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>256</v>
       </c>
-      <c r="Y2" t="s" s="0">
+      <c r="Y2" t="s">
         <v>12</v>
       </c>
-      <c r="Z2" t="s" s="0">
+      <c r="Z2" t="s">
         <v>257</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>212</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>258</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>259</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>40</v>
       </c>
-      <c r="AE2" t="s" s="0">
+      <c r="AE2" t="s">
         <v>260</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>261</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4297,76 +4283,76 @@
       <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>164</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>165</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="E3" t="s">
         <v>262</v>
       </c>
-      <c r="G3" t="s" s="0">
+      <c r="G3" t="s">
         <v>369</v>
       </c>
-      <c r="H3" t="s" s="0">
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s" s="0">
+      <c r="I3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s" s="0">
+      <c r="J3" t="s">
         <v>116</v>
       </c>
-      <c r="K3" t="s" s="0">
+      <c r="K3" t="s">
         <v>117</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>118</v>
       </c>
-      <c r="M3" t="s" s="0">
+      <c r="M3" t="s">
         <v>119</v>
       </c>
-      <c r="N3" t="s" s="0">
+      <c r="N3" t="s">
         <v>99</v>
       </c>
-      <c r="O3" t="s" s="0">
+      <c r="O3" t="s">
         <v>100</v>
       </c>
-      <c r="P3" t="s" s="0">
+      <c r="P3" t="s">
         <v>118</v>
       </c>
-      <c r="Q3" t="s" s="0">
+      <c r="Q3" t="s">
         <v>263</v>
       </c>
-      <c r="R3" t="s" s="0">
+      <c r="R3" t="s">
         <v>112</v>
       </c>
-      <c r="S3" t="s" s="0">
+      <c r="S3" t="s">
         <v>264</v>
       </c>
-      <c r="T3" t="s" s="0">
+      <c r="T3" t="s">
         <v>265</v>
       </c>
-      <c r="U3" t="s" s="0">
+      <c r="U3" t="s">
         <v>266</v>
       </c>
-      <c r="V3" t="s" s="0">
+      <c r="V3" t="s">
         <v>367</v>
       </c>
-      <c r="W3" t="s" s="0">
+      <c r="W3" t="s">
         <v>406</v>
       </c>
-      <c r="X3" t="s" s="0">
+      <c r="X3" t="s">
         <v>267</v>
       </c>
-      <c r="Y3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG3" t="s" s="0">
+      <c r="Y3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4374,76 +4360,76 @@
       <c r="A4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>140</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="D4" t="s">
         <v>141</v>
       </c>
-      <c r="E4" t="s" s="0">
+      <c r="E4" t="s">
         <v>268</v>
       </c>
-      <c r="G4" t="s" s="0">
+      <c r="G4" t="s">
         <v>39</v>
       </c>
-      <c r="H4" t="s" s="0">
+      <c r="H4" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s" s="0">
+      <c r="I4" t="s">
         <v>12</v>
       </c>
-      <c r="J4" t="s" s="0">
+      <c r="J4" t="s">
         <v>269</v>
       </c>
-      <c r="K4" t="s" s="0">
+      <c r="K4" t="s">
         <v>270</v>
       </c>
-      <c r="L4" t="s" s="0">
+      <c r="L4" t="s">
         <v>173</v>
       </c>
-      <c r="M4" t="s" s="0">
+      <c r="M4" t="s">
         <v>174</v>
       </c>
-      <c r="N4" t="s" s="0">
+      <c r="N4" t="s">
         <v>99</v>
       </c>
-      <c r="O4" t="s" s="0">
+      <c r="O4" t="s">
         <v>100</v>
       </c>
-      <c r="P4" t="s" s="0">
+      <c r="P4" t="s">
         <v>173</v>
       </c>
-      <c r="Q4" t="s" s="0">
+      <c r="Q4" t="s">
         <v>271</v>
       </c>
-      <c r="R4" t="s" s="0">
+      <c r="R4" t="s">
         <v>124</v>
       </c>
-      <c r="S4" t="s" s="0">
+      <c r="S4" t="s">
         <v>272</v>
       </c>
-      <c r="T4" t="s" s="0">
+      <c r="T4" t="s">
         <v>273</v>
       </c>
-      <c r="U4" t="s" s="0">
+      <c r="U4" t="s">
         <v>274</v>
       </c>
-      <c r="V4" t="s" s="0">
+      <c r="V4" t="s">
         <v>367</v>
       </c>
-      <c r="W4" t="s" s="0">
+      <c r="W4" t="s">
         <v>406</v>
       </c>
-      <c r="X4" t="s" s="0">
+      <c r="X4" t="s">
         <v>275</v>
       </c>
-      <c r="Y4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG4" t="s" s="0">
+      <c r="Y4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4451,97 +4437,97 @@
       <c r="A5" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s">
         <v>122</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s">
         <v>123</v>
       </c>
-      <c r="E5" t="s" s="0">
+      <c r="E5" t="s">
         <v>276</v>
       </c>
-      <c r="G5" t="s" s="0">
+      <c r="G5" t="s">
         <v>40</v>
       </c>
-      <c r="H5" t="s" s="0">
+      <c r="H5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" t="s" s="0">
+      <c r="I5" t="s">
         <v>12</v>
       </c>
-      <c r="J5" t="s" s="0">
+      <c r="J5" t="s">
         <v>277</v>
       </c>
-      <c r="K5" t="s" s="0">
+      <c r="K5" t="s">
         <v>97</v>
       </c>
-      <c r="L5" t="s" s="0">
+      <c r="L5" t="s">
         <v>131</v>
       </c>
-      <c r="M5" t="s" s="0">
+      <c r="M5" t="s">
         <v>132</v>
       </c>
-      <c r="N5" t="s" s="0">
+      <c r="N5" t="s">
         <v>99</v>
       </c>
-      <c r="O5" t="s" s="0">
+      <c r="O5" t="s">
         <v>100</v>
       </c>
-      <c r="P5" t="s" s="0">
+      <c r="P5" t="s">
         <v>131</v>
       </c>
-      <c r="Q5" t="s" s="0">
+      <c r="Q5" t="s">
         <v>278</v>
       </c>
-      <c r="R5" t="s" s="0">
+      <c r="R5" t="s">
         <v>142</v>
       </c>
-      <c r="S5" t="s" s="0">
+      <c r="S5" t="s">
         <v>279</v>
       </c>
-      <c r="T5" t="s" s="0">
+      <c r="T5" t="s">
         <v>280</v>
       </c>
-      <c r="U5" t="s" s="0">
+      <c r="U5" t="s">
         <v>281</v>
       </c>
-      <c r="V5" t="s" s="0">
+      <c r="V5" t="s">
         <v>367</v>
       </c>
-      <c r="W5" t="s" s="0">
+      <c r="W5" t="s">
         <v>406</v>
       </c>
-      <c r="X5" t="s" s="0">
+      <c r="X5" t="s">
         <v>282</v>
       </c>
-      <c r="Y5" t="s" s="0">
+      <c r="Y5" t="s">
         <v>12</v>
       </c>
-      <c r="Z5" t="s" s="0">
+      <c r="Z5" t="s">
         <v>283</v>
       </c>
-      <c r="AA5" t="s" s="0">
+      <c r="AA5" t="s">
         <v>164</v>
       </c>
-      <c r="AB5" t="s" s="0">
+      <c r="AB5" t="s">
         <v>284</v>
       </c>
-      <c r="AC5" t="s" s="0">
+      <c r="AC5" t="s">
         <v>19</v>
       </c>
-      <c r="AD5" t="s" s="0">
+      <c r="AD5" t="s">
         <v>37</v>
       </c>
-      <c r="AE5" t="s" s="0">
+      <c r="AE5" t="s">
         <v>285</v>
       </c>
-      <c r="AF5" t="s" s="0">
+      <c r="AF5" t="s">
         <v>286</v>
       </c>
-      <c r="AG5" t="s" s="0">
+      <c r="AG5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4549,76 +4535,76 @@
       <c r="A6" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="C6" t="s">
         <v>194</v>
       </c>
-      <c r="D6" t="s" s="0">
+      <c r="D6" t="s">
         <v>195</v>
       </c>
-      <c r="E6" t="s" s="0">
+      <c r="E6" t="s">
         <v>287</v>
       </c>
-      <c r="G6" t="s" s="0">
+      <c r="G6" t="s">
         <v>42</v>
       </c>
-      <c r="H6" t="s" s="0">
+      <c r="H6" t="s">
         <v>19</v>
       </c>
-      <c r="I6" t="s" s="0">
+      <c r="I6" t="s">
         <v>12</v>
       </c>
-      <c r="J6" t="s" s="0">
+      <c r="J6" t="s">
         <v>288</v>
       </c>
-      <c r="K6" t="s" s="0">
+      <c r="K6" t="s">
         <v>289</v>
       </c>
-      <c r="L6" t="s" s="0">
+      <c r="L6" t="s">
         <v>118</v>
       </c>
-      <c r="M6" t="s" s="0">
+      <c r="M6" t="s">
         <v>290</v>
       </c>
-      <c r="N6" t="s" s="0">
+      <c r="N6" t="s">
         <v>99</v>
       </c>
-      <c r="O6" t="s" s="0">
+      <c r="O6" t="s">
         <v>100</v>
       </c>
-      <c r="P6" t="s" s="0">
+      <c r="P6" t="s">
         <v>118</v>
       </c>
-      <c r="Q6" t="s" s="0">
+      <c r="Q6" t="s">
         <v>291</v>
       </c>
-      <c r="R6" t="s" s="0">
+      <c r="R6" t="s">
         <v>166</v>
       </c>
-      <c r="S6" t="s" s="0">
+      <c r="S6" t="s">
         <v>292</v>
       </c>
-      <c r="T6" t="s" s="0">
+      <c r="T6" t="s">
         <v>293</v>
       </c>
-      <c r="U6" t="s" s="0">
+      <c r="U6" t="s">
         <v>294</v>
       </c>
-      <c r="V6" t="s" s="0">
+      <c r="V6" t="s">
         <v>367</v>
       </c>
-      <c r="W6" t="s" s="0">
+      <c r="W6" t="s">
         <v>406</v>
       </c>
-      <c r="X6" t="s" s="0">
+      <c r="X6" t="s">
         <v>295</v>
       </c>
-      <c r="Y6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="s" s="0">
+      <c r="Y6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4626,76 +4612,76 @@
       <c r="A7" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>179</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="C7" t="s">
         <v>211</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="D7" t="s">
         <v>212</v>
       </c>
-      <c r="E7" t="s" s="0">
+      <c r="E7" t="s">
         <v>296</v>
       </c>
-      <c r="G7" t="s" s="0">
+      <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="H7" t="s" s="0">
+      <c r="H7" t="s">
         <v>8</v>
       </c>
-      <c r="I7" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="J7" t="s" s="0">
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" t="s">
         <v>297</v>
       </c>
-      <c r="K7" t="s" s="0">
+      <c r="K7" t="s">
         <v>298</v>
       </c>
-      <c r="L7" t="s" s="0">
+      <c r="L7" t="s">
         <v>150</v>
       </c>
-      <c r="M7" t="s" s="0">
+      <c r="M7" t="s">
         <v>151</v>
       </c>
-      <c r="N7" t="s" s="0">
+      <c r="N7" t="s">
         <v>99</v>
       </c>
-      <c r="O7" t="s" s="0">
+      <c r="O7" t="s">
         <v>100</v>
       </c>
-      <c r="P7" t="s" s="0">
+      <c r="P7" t="s">
         <v>370</v>
       </c>
-      <c r="Q7" t="s" s="0">
+      <c r="Q7" t="s">
         <v>299</v>
       </c>
-      <c r="R7" t="s" s="0">
+      <c r="R7" t="s">
         <v>182</v>
       </c>
-      <c r="S7" t="s" s="0">
+      <c r="S7" t="s">
         <v>300</v>
       </c>
-      <c r="T7" t="s" s="0">
+      <c r="T7" t="s">
         <v>301</v>
       </c>
-      <c r="U7" t="s" s="0">
+      <c r="U7" t="s">
         <v>302</v>
       </c>
-      <c r="V7" t="s" s="0">
+      <c r="V7" t="s">
         <v>367</v>
       </c>
-      <c r="W7" t="s" s="0">
+      <c r="W7" t="s">
         <v>406</v>
       </c>
-      <c r="X7" t="s" s="0">
+      <c r="X7" t="s">
         <v>303</v>
       </c>
-      <c r="Y7" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG7" t="s" s="0">
+      <c r="Y7" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4703,76 +4689,76 @@
       <c r="A8" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>193</v>
       </c>
-      <c r="C8" t="s" s="0">
+      <c r="C8" t="s">
         <v>304</v>
       </c>
-      <c r="D8" t="s" s="0">
+      <c r="D8" t="s">
         <v>305</v>
       </c>
-      <c r="E8" t="s" s="0">
+      <c r="E8" t="s">
         <v>306</v>
       </c>
-      <c r="G8" t="s" s="0">
+      <c r="G8" t="s">
         <v>37</v>
       </c>
-      <c r="H8" t="s" s="0">
+      <c r="H8" t="s">
         <v>11</v>
       </c>
-      <c r="I8" t="s" s="0">
+      <c r="I8" t="s">
         <v>12</v>
       </c>
-      <c r="J8" t="s" s="0">
+      <c r="J8" t="s">
         <v>307</v>
       </c>
-      <c r="K8" t="s" s="0">
+      <c r="K8" t="s">
         <v>308</v>
       </c>
-      <c r="L8" t="s" s="0">
+      <c r="L8" t="s">
         <v>190</v>
       </c>
-      <c r="M8" t="s" s="0">
+      <c r="M8" t="s">
         <v>191</v>
       </c>
-      <c r="N8" t="s" s="0">
+      <c r="N8" t="s">
         <v>99</v>
       </c>
-      <c r="O8" t="s" s="0">
+      <c r="O8" t="s">
         <v>100</v>
       </c>
-      <c r="P8" t="s" s="0">
+      <c r="P8" t="s">
         <v>190</v>
       </c>
-      <c r="Q8" t="s" s="0">
+      <c r="Q8" t="s">
         <v>309</v>
       </c>
-      <c r="R8" t="s" s="0">
+      <c r="R8" t="s">
         <v>196</v>
       </c>
-      <c r="S8" t="s" s="0">
+      <c r="S8" t="s">
         <v>310</v>
       </c>
-      <c r="T8" t="s" s="0">
+      <c r="T8" t="s">
         <v>311</v>
       </c>
-      <c r="U8" t="s" s="0">
+      <c r="U8" t="s">
         <v>312</v>
       </c>
-      <c r="V8" t="s" s="0">
+      <c r="V8" t="s">
         <v>367</v>
       </c>
-      <c r="W8" t="s" s="0">
+      <c r="W8" t="s">
         <v>406</v>
       </c>
-      <c r="X8" t="s" s="0">
+      <c r="X8" t="s">
         <v>313</v>
       </c>
-      <c r="Y8" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AG8" t="s" s="0">
+      <c r="Y8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4780,97 +4766,97 @@
       <c r="A9" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>210</v>
       </c>
-      <c r="C9" t="s" s="0">
+      <c r="C9" t="s">
         <v>314</v>
       </c>
-      <c r="D9" t="s" s="0">
+      <c r="D9" t="s">
         <v>315</v>
       </c>
-      <c r="E9" t="s" s="0">
+      <c r="E9" t="s">
         <v>316</v>
       </c>
-      <c r="G9" t="s" s="0">
+      <c r="G9" t="s">
         <v>39</v>
       </c>
-      <c r="H9" t="s" s="0">
+      <c r="H9" t="s">
         <v>15</v>
       </c>
-      <c r="I9" t="s" s="0">
+      <c r="I9" t="s">
         <v>12</v>
       </c>
-      <c r="J9" t="s" s="0">
+      <c r="J9" t="s">
         <v>317</v>
       </c>
-      <c r="K9" t="s" s="0">
+      <c r="K9" t="s">
         <v>318</v>
       </c>
-      <c r="L9" t="s" s="0">
+      <c r="L9" t="s">
         <v>203</v>
       </c>
-      <c r="M9" t="s" s="0">
+      <c r="M9" t="s">
         <v>319</v>
       </c>
-      <c r="N9" t="s" s="0">
+      <c r="N9" t="s">
         <v>99</v>
       </c>
-      <c r="O9" t="s" s="0">
+      <c r="O9" t="s">
         <v>100</v>
       </c>
-      <c r="P9" t="s" s="0">
+      <c r="P9" t="s">
         <v>203</v>
       </c>
-      <c r="Q9" t="s" s="0">
+      <c r="Q9" t="s">
         <v>320</v>
       </c>
-      <c r="R9" t="s" s="0">
+      <c r="R9" t="s">
         <v>213</v>
       </c>
-      <c r="S9" t="s" s="0">
+      <c r="S9" t="s">
         <v>321</v>
       </c>
-      <c r="T9" t="s" s="0">
+      <c r="T9" t="s">
         <v>322</v>
       </c>
-      <c r="U9" t="s" s="0">
+      <c r="U9" t="s">
         <v>323</v>
       </c>
-      <c r="V9" t="s" s="0">
+      <c r="V9" t="s">
         <v>367</v>
       </c>
-      <c r="W9" t="s" s="0">
+      <c r="W9" t="s">
         <v>407</v>
       </c>
-      <c r="X9" t="s" s="0">
+      <c r="X9" t="s">
         <v>324</v>
       </c>
-      <c r="Y9" t="s" s="0">
+      <c r="Y9" t="s">
         <v>12</v>
       </c>
-      <c r="Z9" t="s" s="0">
+      <c r="Z9" t="s">
         <v>325</v>
       </c>
-      <c r="AA9" t="s" s="0">
+      <c r="AA9" t="s">
         <v>90</v>
       </c>
-      <c r="AB9" t="s" s="0">
+      <c r="AB9" t="s">
         <v>326</v>
       </c>
-      <c r="AC9" t="s" s="0">
+      <c r="AC9" t="s">
         <v>327</v>
       </c>
-      <c r="AD9" t="s" s="0">
+      <c r="AD9" t="s">
         <v>39</v>
       </c>
-      <c r="AE9" t="s" s="0">
+      <c r="AE9" t="s">
         <v>328</v>
       </c>
-      <c r="AF9" t="s" s="0">
+      <c r="AF9" t="s">
         <v>329</v>
       </c>
-      <c r="AG9" t="s" s="0">
+      <c r="AG9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4884,89 +4870,89 @@
   <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="34.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="11.36328125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="3.81640625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="8.36328125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="7.90625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.54296875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="7.36328125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="11.6328125"/>
-    <col min="17" max="18" bestFit="true" customWidth="true" width="8.81640625"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="12.90625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="10.54296875"/>
+    <col min="1" max="2" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>241</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>330</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>331</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>332</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>333</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>334</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>335</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>336</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>337</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>338</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>375</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>380</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>381</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>382</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="S1" t="s">
         <v>81</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="T1" t="s">
         <v>385</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="U1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -4974,43 +4960,43 @@
       <c r="A2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="D2" s="0">
+      <c r="C2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D2">
         <v>8925535099</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>416</v>
       </c>
-      <c r="H2" t="s" s="0">
-        <v>457</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="N2" t="s" s="0">
+      <c r="H2" t="s">
+        <v>456</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" t="s">
         <v>339</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>388</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>383</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>384</v>
       </c>
       <c r="S2" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="T2" t="s" s="0">
+      <c r="T2" t="s">
         <v>383</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>383</v>
       </c>
     </row>
@@ -5018,40 +5004,40 @@
       <c r="A3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="D3" s="0">
+      <c r="C3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D3">
         <v>8925535099</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="E3" t="s">
         <v>417</v>
       </c>
-      <c r="H3" t="s" s="0">
+      <c r="H3" t="s">
         <v>140</v>
       </c>
-      <c r="I3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="N3" t="s" s="0">
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" t="s">
         <v>339</v>
       </c>
-      <c r="O3" s="0">
+      <c r="O3">
         <v>20000</v>
       </c>
-      <c r="P3" t="s" s="0">
-        <v>425</v>
+      <c r="P3" t="s">
+        <v>424</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="T3" t="s" s="0">
+        <v>430</v>
+      </c>
+      <c r="T3" t="s">
         <v>383</v>
       </c>
-      <c r="U3" t="s" s="0">
+      <c r="U3" t="s">
         <v>383</v>
       </c>
     </row>
@@ -5064,385 +5050,379 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.90625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="6.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="14.54296875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="20.08984375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.7265625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="7.54296875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="5.81640625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.08984375"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="9.36328125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="4.81640625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="6.26953125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="6.81640625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="10.54296875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.08984375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="7.90625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="10.36328125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.81640625"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="10.6328125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="12.54296875"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="8.54296875"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="9.26953125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="10.36328125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="7.54296875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="11.81640625"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="19.81640625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="6.81640625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" width="5.81640625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="11.6328125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="8.81640625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="38" max="38" bestFit="true" customWidth="true" width="12.90625"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="10.54296875"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="34.1796875"/>
+    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="34.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>340</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>341</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>241</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>342</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>343</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>344</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>345</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>346</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>347</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>348</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>349</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>350</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>351</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>352</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>353</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="S1" t="s">
         <v>354</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="T1" t="s">
         <v>355</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="U1" t="s">
         <v>356</v>
       </c>
-      <c r="V1" t="s" s="0">
+      <c r="V1" t="s">
         <v>357</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="W1" t="s">
         <v>358</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="X1" t="s">
         <v>359</v>
       </c>
-      <c r="Y1" t="s" s="0">
+      <c r="Y1" t="s">
         <v>360</v>
       </c>
-      <c r="Z1" t="s" s="0">
+      <c r="Z1" t="s">
         <v>361</v>
       </c>
-      <c r="AA1" t="s" s="0">
+      <c r="AA1" t="s">
         <v>362</v>
       </c>
-      <c r="AB1" t="s" s="0">
+      <c r="AB1" t="s">
         <v>371</v>
       </c>
-      <c r="AC1" t="s" s="0">
+      <c r="AC1" t="s">
         <v>372</v>
       </c>
-      <c r="AD1" t="s" s="0">
+      <c r="AD1" t="s">
         <v>373</v>
       </c>
-      <c r="AE1" t="s" s="0">
+      <c r="AE1" t="s">
         <v>376</v>
       </c>
-      <c r="AF1" t="s" s="0">
+      <c r="AF1" t="s">
         <v>374</v>
       </c>
-      <c r="AG1" t="s" s="0">
+      <c r="AG1" t="s">
         <v>377</v>
       </c>
-      <c r="AH1" t="s" s="0">
+      <c r="AH1" t="s">
         <v>379</v>
       </c>
-      <c r="AI1" t="s" s="0">
+      <c r="AI1" t="s">
         <v>380</v>
       </c>
-      <c r="AJ1" t="s" s="0">
+      <c r="AJ1" t="s">
         <v>381</v>
       </c>
-      <c r="AK1" t="s" s="0">
+      <c r="AK1" t="s">
         <v>382</v>
       </c>
-      <c r="AL1" t="s" s="0">
+      <c r="AL1" t="s">
         <v>81</v>
       </c>
-      <c r="AM1" t="s" s="0">
+      <c r="AM1" t="s">
         <v>385</v>
       </c>
-      <c r="AN1" t="s" s="0">
+      <c r="AN1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
-        <v>378</v>
-      </c>
-      <c r="B2" t="s" s="0">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A2" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>363</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E2" t="s">
         <v>459</v>
       </c>
-      <c r="E2" t="s" s="0">
-        <v>461</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>457</v>
-      </c>
-      <c r="G2" s="0">
+      <c r="F2" t="s">
+        <v>456</v>
+      </c>
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>364</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>365</v>
       </c>
-      <c r="M2" s="0">
+      <c r="M2">
         <v>20310</v>
       </c>
-      <c r="N2" s="0">
+      <c r="N2">
         <v>7000</v>
       </c>
-      <c r="O2" s="0">
+      <c r="O2">
         <v>73831</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="2"/>
-      <c r="U2" s="0">
+      <c r="U2">
         <v>0</v>
       </c>
-      <c r="V2" t="s" s="0">
+      <c r="V2" t="s">
         <v>12</v>
       </c>
       <c r="W2" s="2">
         <v>46168</v>
       </c>
-      <c r="X2" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="Y2" s="0">
+      <c r="X2" t="s">
+        <v>462</v>
+      </c>
+      <c r="Y2">
         <v>93211</v>
       </c>
-      <c r="Z2" s="0">
+      <c r="Z2">
         <v>2093003</v>
       </c>
-      <c r="AA2" s="0">
+      <c r="AA2">
         <v>3000</v>
       </c>
-      <c r="AB2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AD2" s="0">
+      <c r="AB2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD2">
         <v>0</v>
       </c>
-      <c r="AE2" s="0">
+      <c r="AE2">
         <v>0</v>
       </c>
-      <c r="AF2" t="s" s="0">
-        <v>456</v>
-      </c>
-      <c r="AG2" s="0">
+      <c r="AF2" t="s">
+        <v>455</v>
+      </c>
+      <c r="AG2">
         <v>10000</v>
       </c>
-      <c r="AH2" t="s" s="0">
-        <v>458</v>
-      </c>
-      <c r="AI2" t="s" s="0">
-        <v>425</v>
-      </c>
-      <c r="AJ2" t="s" s="0">
+      <c r="AH2" t="s">
+        <v>467</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>424</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>443</v>
+      </c>
+      <c r="AK2" t="s">
         <v>444</v>
       </c>
-      <c r="AK2" t="s" s="0">
-        <v>445</v>
-      </c>
       <c r="AL2" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="AM2" t="s" s="0">
+        <v>430</v>
+      </c>
+      <c r="AM2" t="s">
         <v>383</v>
       </c>
-      <c r="AN2" t="s" s="0">
+      <c r="AN2" t="s">
         <v>383</v>
       </c>
-      <c r="AQ2" t="s" s="0">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
-      <c r="A3" s="44" t="s">
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>437</v>
+      <c r="B3" t="s">
+        <v>436</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
+        <v>458</v>
+      </c>
+      <c r="E3" t="s">
         <v>460</v>
       </c>
-      <c r="E3" t="s" s="0">
-        <v>462</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>457</v>
-      </c>
-      <c r="G3" s="0">
+      <c r="F3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" s="0">
+      <c r="H3">
         <v>8000</v>
       </c>
-      <c r="I3" t="s" s="0">
+      <c r="I3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s" s="0">
+      <c r="J3" t="s">
         <v>364</v>
       </c>
-      <c r="K3" t="s" s="0">
+      <c r="K3" t="s">
         <v>365</v>
       </c>
-      <c r="M3" s="0">
+      <c r="M3">
         <v>20311</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3">
         <v>12000</v>
       </c>
-      <c r="O3" s="0">
+      <c r="O3">
         <v>73832</v>
       </c>
-      <c r="P3" t="s" s="0">
+      <c r="P3" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="2"/>
-      <c r="U3" s="0">
+      <c r="U3">
         <v>0</v>
       </c>
-      <c r="V3" t="s" s="0">
+      <c r="V3" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="2">
         <v>46169</v>
       </c>
-      <c r="X3" t="s" s="0">
-        <v>465</v>
-      </c>
-      <c r="Y3" s="0">
+      <c r="X3" t="s">
+        <v>462</v>
+      </c>
+      <c r="Y3">
         <v>93211</v>
       </c>
-      <c r="Z3" s="0">
+      <c r="Z3">
         <v>2093004</v>
       </c>
-      <c r="AA3" s="0">
+      <c r="AA3">
         <v>10000</v>
       </c>
-      <c r="AB3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="AD3" s="0">
+      <c r="AB3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3">
         <v>0</v>
       </c>
-      <c r="AE3" s="0">
+      <c r="AE3">
         <v>0</v>
       </c>
-      <c r="AF3" t="s" s="0">
-        <v>456</v>
-      </c>
-      <c r="AG3" s="0">
+      <c r="AF3" t="s">
+        <v>455</v>
+      </c>
+      <c r="AG3">
         <v>30000</v>
       </c>
-      <c r="AH3" t="s" s="0">
-        <v>466</v>
-      </c>
-      <c r="AI3" t="s" s="0">
-        <v>426</v>
-      </c>
-      <c r="AJ3" t="s" s="0">
+      <c r="AH3" t="s">
+        <v>463</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>425</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>445</v>
+      </c>
+      <c r="AK3" t="s">
         <v>446</v>
       </c>
-      <c r="AK3" t="s" s="0">
-        <v>447</v>
-      </c>
       <c r="AL3" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="AM3" t="s" s="0">
+        <v>431</v>
+      </c>
+      <c r="AM3" t="s">
         <v>383</v>
       </c>
-      <c r="AN3" t="s" s="0">
+      <c r="AN3" t="s">
         <v>383</v>
-      </c>
-      <c r="AQ3" t="s" s="0">
-        <v>418</v>
       </c>
     </row>
   </sheetData>
